--- a/questionnaire_templates/043_europassport_eligibility_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/043_europassport_eligibility_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'label':_'irish_citizenship'}</t>
+          <t>irish_citizenship</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'label': 'Irish Citizenship'}</t>
+          <t>Irish Citizenship</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2.2,_'label':_'british_citizenship'}</t>
+          <t>british_citizenship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2.2, 'label': 'British Citizenship'}</t>
+          <t>British Citizenship</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2.3,_'label':_'spanish_citizenship'}</t>
+          <t>spanish_citizenship</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2.3, 'label': 'Spanish Citizenship'}</t>
+          <t>Spanish Citizenship</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'label':_'6_months'}</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'label': '6 months'}</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'label':_'1_year'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'label': '1 year'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'label':_'2_years'}</t>
+          <t>2_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'label': '2 years'}</t>
+          <t>2 years</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4.4,_'label':_'3_years'}</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4.4, 'label': '3 years'}</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4.5,_'label':_'4_years'}</t>
+          <t>4_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4.5, 'label': '4 years'}</t>
+          <t>4 years</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5.4,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5.4, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5.5,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5.5, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'label': 'High school'}</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_6.4,_'label':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 6.4, 'label': 'PhD'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_6.5,_'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 6.5, 'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_6.6,_'label':_'diploma'}</t>
+          <t>diploma</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 6.6, 'label': 'Diploma'}</t>
+          <t>Diploma</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'label':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'label': 'Self-employed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_9.4,_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 9.4, 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_9.5,_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 9.5, 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'label':_'employment_income'}</t>
+          <t>employment_income</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'label': 'Employment Income'}</t>
+          <t>Employment Income</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'label':_'self-employment_income'}</t>
+          <t>self-employment_income</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'label': 'Self-employment Income'}</t>
+          <t>Self-employment Income</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'label':_'social_security_benefits'}</t>
+          <t>social_security_benefits</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'label': 'Social Security Benefits'}</t>
+          <t>Social Security Benefits</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_10.4,_'label':_'government_grant'}</t>
+          <t>government_grant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 10.4, 'label': 'Government Grant'}</t>
+          <t>Government Grant</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_10.5,_'label':_'investment_income'}</t>
+          <t>investment_income</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 10.5, 'label': 'Investment Income'}</t>
+          <t>Investment Income</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_10.6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 10.6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_12.1,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 12.1, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_12.2,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 12.2, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_12.3,_'label':_'undisclosed'}</t>
+          <t>undisclosed</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 12.3, 'label': 'Undisclosed'}</t>
+          <t>Undisclosed</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_13.3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 13.3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_14.1,_'label':_'passport'}</t>
+          <t>passport</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 14.1, 'label': 'Passport'}</t>
+          <t>Passport</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_14.2,_'label':_'id_card'}</t>
+          <t>id_card</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 14.2, 'label': 'ID Card'}</t>
+          <t>ID Card</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_14.3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 14.3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_14.4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 14.4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'within_the_eu'}</t>
+          <t>within_the_eu</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'Within the EU'}</t>
+          <t>Within the EU</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'label':_'outside_the_eu'}</t>
+          <t>outside_the_eu</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'label': 'Outside the EU'}</t>
+          <t>Outside the EU</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_16.3,_'label':_'undetermined'}</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 16.3, 'label': 'Undetermined'}</t>
+          <t>Undetermined</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_16.4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 16.4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_18.1,_'label':_'machine_readable'}</t>
+          <t>machine_readable</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 18.1, 'label': 'Machine Readable'}</t>
+          <t>Machine Readable</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_18.2,_'label':_'non-machine_readable'}</t>
+          <t>non-machine_readable</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 18.2, 'label': 'Non-Machine Readable'}</t>
+          <t>Non-Machine Readable</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_18.3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 18.3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_18.4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 18.4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
